--- a/Team-Data/2013-14/2-13-2013-14.xlsx
+++ b/Team-Data/2013-14/2-13-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
@@ -751,7 +818,7 @@
         <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
@@ -808,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.471</v>
+        <v>0.48</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="J4" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
         <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T4" t="n">
-        <v>39.1</v>
+        <v>39.4</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
         <v>14.5</v>
@@ -1088,7 +1155,7 @@
         <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" t="n">
         <v>22.2</v>
@@ -1097,22 +1164,22 @@
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1133,13 +1200,13 @@
         <v>13</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
         <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
@@ -1175,10 +1242,10 @@
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
@@ -1336,7 +1403,7 @@
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.519</v>
+        <v>0.51</v>
       </c>
       <c r="H6" t="n">
         <v>48.8</v>
@@ -1407,19 +1474,19 @@
         <v>34.3</v>
       </c>
       <c r="J6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L6" t="n">
         <v>5.9</v>
       </c>
       <c r="M6" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O6" t="n">
         <v>17.8</v>
@@ -1428,34 +1495,34 @@
         <v>23.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T6" t="n">
         <v>44.8</v>
       </c>
       <c r="U6" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V6" t="n">
         <v>15.7</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
         <v>21.1</v>
@@ -1464,10 +1531,10 @@
         <v>92.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1488,7 +1555,7 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1518,7 +1585,7 @@
         <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
         <v>26</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1737,7 @@
         <v>5</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>19</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>19</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2692,7 @@
         <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>0.34</v>
+        <v>0.346</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
         <v>84</v>
@@ -3051,37 +3118,37 @@
         <v>0.442</v>
       </c>
       <c r="L15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M15" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="N15" t="n">
         <v>0.371</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P15" t="n">
         <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="R15" t="n">
         <v>9.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
         <v>42.4</v>
       </c>
       <c r="U15" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
         <v>6.6</v>
@@ -3090,7 +3157,7 @@
         <v>5.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z15" t="n">
         <v>20.1</v>
@@ -3099,13 +3166,13 @@
         <v>19.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="AC15" t="n">
         <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3120,7 +3187,7 @@
         <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ15" t="n">
         <v>10</v>
@@ -3132,7 +3199,7 @@
         <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN15" t="n">
         <v>8</v>
@@ -3144,13 +3211,13 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>20</v>
@@ -3159,7 +3226,7 @@
         <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3168,13 +3235,13 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,7 +3548,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
         <v>6</v>
@@ -3496,7 +3563,7 @@
         <v>11</v>
       </c>
       <c r="AM17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN17" t="n">
         <v>10</v>
@@ -3508,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3678,7 +3745,7 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3909,7 @@
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
         <v>25</v>
@@ -3878,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4227,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4269,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.782</v>
+        <v>0.778</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
@@ -4319,37 +4386,37 @@
         <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L22" t="n">
         <v>7.4</v>
       </c>
       <c r="M22" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O22" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="P22" t="n">
         <v>24.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.804</v>
+        <v>0.802</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S22" t="n">
         <v>34.4</v>
       </c>
       <c r="T22" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U22" t="n">
         <v>21.6</v>
@@ -4358,7 +4425,7 @@
         <v>15.7</v>
       </c>
       <c r="W22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X22" t="n">
         <v>6.2</v>
@@ -4367,19 +4434,19 @@
         <v>3.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>105</v>
+        <v>104.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4397,7 +4464,7 @@
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4406,10 +4473,10 @@
         <v>17</v>
       </c>
       <c r="AM22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4421,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4579,7 +4646,7 @@
         <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4794,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4979,7 +5046,7 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -5295,16 +5362,16 @@
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
         <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5716,7 +5783,7 @@
         <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>28</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
@@ -5877,7 +5944,7 @@
         <v>20</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
@@ -6092,7 +6159,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-13-2013-14</t>
+          <t>2014-02-13</t>
         </is>
       </c>
     </row>
